--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R01-EnsembleSavoirFaire-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R01-EnsembleSavoirFaire-CISIS.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1060" uniqueCount="725">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1064" uniqueCount="729">
   <si>
     <t>Property</t>
   </si>
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260730120000</t>
+    <t>20260928120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:00:00+01:00</t>
+    <t>2026-09-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1213,34 +1213,46 @@
     <t>SI01</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée pathologies chroniques stabilisées (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Pathologies chroniques stabilisées (SI)</t>
+  </si>
+  <si>
+    <t>Suivi des patients chroniques (diabète, HTA, insuffisance cardiaque...), prévention, coordination des parcours, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>SI02</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée oncologie et hémato-oncologie (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Oncologie et hémato-oncologie (SI)</t>
+  </si>
+  <si>
+    <t>Prise en charge des cancers et maladies du sang, administration de traitements, gestion des effets secondaires, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>SI03</t>
   </si>
   <si>
-    <t>Exerc. infirmier pratique avancée maladie rénale chroniq., dialyse, transp. rénale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Maladie rénale chronique, dialyse, transplantation rénale (SI)</t>
+  </si>
+  <si>
+    <t>Suivi des patients insuffisants rénaux, gestion de la dialyse, accompagnement à la transplantation, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>SI04</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée santé mentale (SI)</t>
+    <t>Infirmier(ère) en pratique avancée Psychiatrie et santé mentale (SI)</t>
+  </si>
+  <si>
+    <t>Suivi des troubles psychiatriques, entretiens cliniques, prescription de psychotropes, coordination des soins, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>SI05</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée urgences (SI)</t>
-  </si>
-  <si>
-    <t>Le décret n°2021-1384 du 25 octobre 2021 relatif à l'exercice en pratique avancée de la profession d'infirmiers (IPA) dans le domaine d'intervention des urgences a inscrit les « urgences » comme nouveau domaine d'intervention de l'infirmier en pratique avancé. C'est le 5e domaine d'exercice des IPA ainsi acté (après pathologies chroniques stabilisées ; oncologie et hémato-oncologie ; maladie rénale chronique, dialyse et transplantation rénale ; santé mentale).</t>
+    <t>Infirmier(ère) en pratique avancée Urgences (SI)</t>
+  </si>
+  <si>
+    <t>Prise en charge des situations d'urgence, gestes techniques, gestion du stress, collaboration avec urgentistes, en complémentarité avec le médecin et les autres professionnels de santé.</t>
   </si>
   <si>
     <t>SI06</t>
@@ -4647,56 +4659,64 @@
       <c r="C170" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="D170" s="2"/>
+      <c r="D170" t="s" s="2">
+        <v>400</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="D171" s="2"/>
+        <v>402</v>
+      </c>
+      <c r="D171" t="s" s="2">
+        <v>403</v>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="D172" s="2"/>
+        <v>405</v>
+      </c>
+      <c r="D172" t="s" s="2">
+        <v>406</v>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="D173" s="2"/>
+        <v>408</v>
+      </c>
+      <c r="D173" t="s" s="2">
+        <v>409</v>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
         <v>61</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D174" t="s" s="2">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="175">
@@ -4704,13 +4724,13 @@
         <v>61</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D175" t="s" s="2">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="176">
@@ -4718,13 +4738,13 @@
         <v>61</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D176" t="s" s="2">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="177">
@@ -4732,13 +4752,13 @@
         <v>61</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="D177" t="s" s="2">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="178">
@@ -4746,13 +4766,13 @@
         <v>61</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="C178" t="s" s="2">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D178" t="s" s="2">
-        <v>420</v>
+        <v>424</v>
       </c>
     </row>
     <row r="179">
@@ -4760,10 +4780,10 @@
         <v>61</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C179" t="s" s="2">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="D179" s="2"/>
     </row>
@@ -4772,10 +4792,10 @@
         <v>61</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="C180" t="s" s="2">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D180" s="2"/>
     </row>
@@ -4784,10 +4804,10 @@
         <v>61</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C181" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="D181" s="2"/>
     </row>
@@ -4796,10 +4816,10 @@
         <v>61</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="C182" t="s" s="2">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="D182" s="2"/>
     </row>
@@ -4808,10 +4828,10 @@
         <v>61</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="C183" t="s" s="2">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="D183" s="2"/>
     </row>
@@ -4820,10 +4840,10 @@
         <v>61</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="C184" t="s" s="2">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="D184" s="2"/>
     </row>
@@ -4832,10 +4852,10 @@
         <v>61</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="C185" t="s" s="2">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="D185" s="2"/>
     </row>
@@ -4844,10 +4864,10 @@
         <v>61</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="C186" t="s" s="2">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="D186" s="2"/>
     </row>
@@ -4856,10 +4876,10 @@
         <v>61</v>
       </c>
       <c r="B187" t="s" s="2">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C187" t="s" s="2">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D187" s="2"/>
     </row>
@@ -4868,10 +4888,10 @@
         <v>61</v>
       </c>
       <c r="B188" t="s" s="2">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="C188" t="s" s="2">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="D188" s="2"/>
     </row>
@@ -4880,10 +4900,10 @@
         <v>61</v>
       </c>
       <c r="B189" t="s" s="2">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C189" t="s" s="2">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D189" s="2"/>
     </row>
@@ -4892,10 +4912,10 @@
         <v>61</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="C190" t="s" s="2">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="D190" s="2"/>
     </row>
@@ -4904,10 +4924,10 @@
         <v>61</v>
       </c>
       <c r="B191" t="s" s="2">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="C191" t="s" s="2">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="D191" s="2"/>
     </row>
@@ -4916,10 +4936,10 @@
         <v>61</v>
       </c>
       <c r="B192" t="s" s="2">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="C192" t="s" s="2">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="D192" s="2"/>
     </row>
@@ -4928,10 +4948,10 @@
         <v>61</v>
       </c>
       <c r="B193" t="s" s="2">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C193" t="s" s="2">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D193" s="2"/>
     </row>
@@ -4940,10 +4960,10 @@
         <v>61</v>
       </c>
       <c r="B194" t="s" s="2">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="C194" t="s" s="2">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="D194" s="2"/>
     </row>
@@ -4952,10 +4972,10 @@
         <v>61</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="C195" t="s" s="2">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="D195" s="2"/>
     </row>
@@ -4964,10 +4984,10 @@
         <v>61</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="C196" t="s" s="2">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="D196" s="2"/>
     </row>
@@ -4976,10 +4996,10 @@
         <v>61</v>
       </c>
       <c r="B197" t="s" s="2">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="C197" t="s" s="2">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="D197" s="2"/>
     </row>
@@ -4988,10 +5008,10 @@
         <v>61</v>
       </c>
       <c r="B198" t="s" s="2">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="C198" t="s" s="2">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="D198" s="2"/>
     </row>
@@ -5000,10 +5020,10 @@
         <v>61</v>
       </c>
       <c r="B199" t="s" s="2">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="C199" t="s" s="2">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="D199" s="2"/>
     </row>
@@ -5012,10 +5032,10 @@
         <v>61</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="C200" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="D200" s="2"/>
     </row>
@@ -5024,10 +5044,10 @@
         <v>61</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="C201" t="s" s="2">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="D201" s="2"/>
     </row>
@@ -5036,10 +5056,10 @@
         <v>61</v>
       </c>
       <c r="B202" t="s" s="2">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="C202" t="s" s="2">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="D202" s="2"/>
     </row>
@@ -5048,10 +5068,10 @@
         <v>61</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C203" t="s" s="2">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D203" s="2"/>
     </row>
@@ -5060,10 +5080,10 @@
         <v>61</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="C204" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="D204" s="2"/>
     </row>
@@ -5072,10 +5092,10 @@
         <v>61</v>
       </c>
       <c r="B205" t="s" s="2">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="C205" t="s" s="2">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="D205" s="2"/>
     </row>
@@ -5084,10 +5104,10 @@
         <v>61</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D206" s="2"/>
     </row>
@@ -5096,10 +5116,10 @@
         <v>61</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="D207" s="2"/>
     </row>
@@ -5108,10 +5128,10 @@
         <v>61</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="D208" s="2"/>
     </row>
@@ -5120,10 +5140,10 @@
         <v>61</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D209" s="2"/>
     </row>
@@ -5132,10 +5152,10 @@
         <v>61</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="D210" s="2"/>
     </row>
@@ -5144,10 +5164,10 @@
         <v>61</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="D211" s="2"/>
     </row>
@@ -5156,10 +5176,10 @@
         <v>61</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D212" s="2"/>
     </row>
@@ -5168,10 +5188,10 @@
         <v>61</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="D213" s="2"/>
     </row>
@@ -5180,10 +5200,10 @@
         <v>61</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D214" s="2"/>
     </row>
@@ -5192,10 +5212,10 @@
         <v>61</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D215" s="2"/>
     </row>
@@ -5204,10 +5224,10 @@
         <v>61</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D216" s="2"/>
     </row>
@@ -5216,10 +5236,10 @@
         <v>61</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="D217" s="2"/>
     </row>
@@ -5228,10 +5248,10 @@
         <v>61</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D218" s="2"/>
     </row>
@@ -5240,10 +5260,10 @@
         <v>61</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D219" s="2"/>
     </row>
@@ -5252,10 +5272,10 @@
         <v>61</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="D220" s="2"/>
     </row>
@@ -5264,10 +5284,10 @@
         <v>61</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D221" s="2"/>
     </row>
@@ -5276,10 +5296,10 @@
         <v>61</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D222" s="2"/>
     </row>
@@ -5288,10 +5308,10 @@
         <v>61</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="D223" s="2"/>
     </row>
@@ -5300,10 +5320,10 @@
         <v>61</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D224" s="2"/>
     </row>
@@ -5312,10 +5332,10 @@
         <v>61</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D225" s="2"/>
     </row>
@@ -5324,10 +5344,10 @@
         <v>61</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="D226" s="2"/>
     </row>
@@ -5336,10 +5356,10 @@
         <v>61</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="D227" s="2"/>
     </row>
@@ -5348,10 +5368,10 @@
         <v>61</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D228" s="2"/>
     </row>
@@ -5360,10 +5380,10 @@
         <v>61</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="D229" s="2"/>
     </row>
@@ -5372,10 +5392,10 @@
         <v>61</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="D230" s="2"/>
     </row>
@@ -5384,10 +5404,10 @@
         <v>61</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D231" s="2"/>
     </row>
@@ -5396,10 +5416,10 @@
         <v>61</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="D232" s="2"/>
     </row>
@@ -5408,10 +5428,10 @@
         <v>61</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="D233" s="2"/>
     </row>
@@ -5420,10 +5440,10 @@
         <v>61</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D234" s="2"/>
     </row>
@@ -5432,10 +5452,10 @@
         <v>61</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="D235" s="2"/>
     </row>
@@ -5444,10 +5464,10 @@
         <v>61</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D236" s="2"/>
     </row>
@@ -5456,10 +5476,10 @@
         <v>61</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D237" s="2"/>
     </row>
@@ -5468,10 +5488,10 @@
         <v>61</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="D238" s="2"/>
     </row>
@@ -5480,10 +5500,10 @@
         <v>61</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="D239" s="2"/>
     </row>
@@ -5492,10 +5512,10 @@
         <v>61</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D240" s="2"/>
     </row>
@@ -5504,10 +5524,10 @@
         <v>61</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="D241" s="2"/>
     </row>
@@ -5516,10 +5536,10 @@
         <v>61</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="D242" s="2"/>
     </row>
@@ -5528,10 +5548,10 @@
         <v>61</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="D243" s="2"/>
     </row>
@@ -5540,10 +5560,10 @@
         <v>61</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="D244" s="2"/>
     </row>
@@ -5552,10 +5572,10 @@
         <v>61</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="D245" s="2"/>
     </row>
@@ -5564,10 +5584,10 @@
         <v>61</v>
       </c>
       <c r="B246" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="C246" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D246" s="2"/>
     </row>
@@ -5576,10 +5596,10 @@
         <v>61</v>
       </c>
       <c r="B247" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="C247" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="D247" s="2"/>
     </row>
@@ -5588,10 +5608,10 @@
         <v>61</v>
       </c>
       <c r="B248" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="C248" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D248" s="2"/>
     </row>
@@ -5600,10 +5620,10 @@
         <v>61</v>
       </c>
       <c r="B249" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C249" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="D249" s="2"/>
     </row>
@@ -5612,10 +5632,10 @@
         <v>61</v>
       </c>
       <c r="B250" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="C250" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="D250" s="2"/>
     </row>
@@ -5624,10 +5644,10 @@
         <v>61</v>
       </c>
       <c r="B251" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="C251" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="D251" s="2"/>
     </row>
@@ -5636,10 +5656,10 @@
         <v>61</v>
       </c>
       <c r="B252" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="C252" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="D252" s="2"/>
     </row>
@@ -5648,10 +5668,10 @@
         <v>61</v>
       </c>
       <c r="B253" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="C253" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="D253" s="2"/>
     </row>
@@ -5660,10 +5680,10 @@
         <v>61</v>
       </c>
       <c r="B254" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="C254" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="D254" s="2"/>
     </row>
@@ -5672,10 +5692,10 @@
         <v>61</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D255" s="2"/>
     </row>
@@ -5684,10 +5704,10 @@
         <v>61</v>
       </c>
       <c r="B256" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="C256" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="D256" s="2"/>
     </row>
@@ -5696,10 +5716,10 @@
         <v>61</v>
       </c>
       <c r="B257" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="C257" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="D257" s="2"/>
     </row>
@@ -5708,10 +5728,10 @@
         <v>61</v>
       </c>
       <c r="B258" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="C258" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="D258" s="2"/>
     </row>
@@ -5720,10 +5740,10 @@
         <v>61</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="D259" s="2"/>
     </row>
@@ -5732,10 +5752,10 @@
         <v>61</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="D260" s="2"/>
     </row>
@@ -5744,10 +5764,10 @@
         <v>61</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="D261" s="2"/>
     </row>
@@ -5756,10 +5776,10 @@
         <v>61</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="D262" s="2"/>
     </row>
@@ -5768,10 +5788,10 @@
         <v>61</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="D263" s="2"/>
     </row>
@@ -5780,10 +5800,10 @@
         <v>61</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="D264" s="2"/>
     </row>
@@ -5792,10 +5812,10 @@
         <v>61</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="D265" s="2"/>
     </row>
@@ -5804,10 +5824,10 @@
         <v>61</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="D266" s="2"/>
     </row>
@@ -5816,10 +5836,10 @@
         <v>61</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="D267" s="2"/>
     </row>
@@ -5828,10 +5848,10 @@
         <v>61</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="D268" s="2"/>
     </row>
@@ -5840,10 +5860,10 @@
         <v>61</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="D269" s="2"/>
     </row>
@@ -5852,10 +5872,10 @@
         <v>61</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="D270" s="2"/>
     </row>
@@ -5864,10 +5884,10 @@
         <v>61</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="D271" s="2"/>
     </row>
@@ -5876,10 +5896,10 @@
         <v>61</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D272" s="2"/>
     </row>
@@ -5888,10 +5908,10 @@
         <v>61</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="D273" s="2"/>
     </row>
@@ -5900,10 +5920,10 @@
         <v>61</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="D274" s="2"/>
     </row>
@@ -5912,10 +5932,10 @@
         <v>61</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="D275" s="2"/>
     </row>
@@ -5924,10 +5944,10 @@
         <v>61</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="D276" s="2"/>
     </row>
@@ -5936,10 +5956,10 @@
         <v>61</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="D277" s="2"/>
     </row>
@@ -5948,10 +5968,10 @@
         <v>61</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="D278" s="2"/>
     </row>
@@ -5960,10 +5980,10 @@
         <v>61</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="D279" s="2"/>
     </row>
@@ -5972,10 +5992,10 @@
         <v>61</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="D280" s="2"/>
     </row>
@@ -5984,10 +6004,10 @@
         <v>61</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="D281" s="2"/>
     </row>
@@ -5996,10 +6016,10 @@
         <v>61</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="D282" s="2"/>
     </row>
@@ -6008,10 +6028,10 @@
         <v>61</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="D283" s="2"/>
     </row>
@@ -6020,10 +6040,10 @@
         <v>61</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="D284" s="2"/>
     </row>
@@ -6032,10 +6052,10 @@
         <v>61</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="D285" s="2"/>
     </row>
@@ -6044,10 +6064,10 @@
         <v>61</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="D286" s="2"/>
     </row>
@@ -6056,10 +6076,10 @@
         <v>61</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="D287" s="2"/>
     </row>
@@ -6068,10 +6088,10 @@
         <v>61</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D288" s="2"/>
     </row>
@@ -6080,10 +6100,10 @@
         <v>61</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="D289" s="2"/>
     </row>
@@ -6092,10 +6112,10 @@
         <v>61</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="D290" s="2"/>
     </row>
@@ -6104,10 +6124,10 @@
         <v>61</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="D291" s="2"/>
     </row>
@@ -6116,10 +6136,10 @@
         <v>61</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="D292" s="2"/>
     </row>
@@ -6128,10 +6148,10 @@
         <v>61</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="D293" s="2"/>
     </row>
@@ -6140,10 +6160,10 @@
         <v>61</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D294" s="2"/>
     </row>
@@ -6152,10 +6172,10 @@
         <v>61</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="D295" s="2"/>
     </row>
@@ -6164,10 +6184,10 @@
         <v>61</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="D296" s="2"/>
     </row>
@@ -6176,10 +6196,10 @@
         <v>61</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="D297" s="2"/>
     </row>
@@ -6188,10 +6208,10 @@
         <v>61</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="D298" s="2"/>
     </row>
@@ -6200,10 +6220,10 @@
         <v>61</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="D299" s="2"/>
     </row>
@@ -6212,10 +6232,10 @@
         <v>61</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="D300" s="2"/>
     </row>
@@ -6224,10 +6244,10 @@
         <v>61</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="D301" s="2"/>
     </row>
@@ -6236,10 +6256,10 @@
         <v>61</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="D302" s="2"/>
     </row>
@@ -6248,10 +6268,10 @@
         <v>61</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="D303" s="2"/>
     </row>
@@ -6260,10 +6280,10 @@
         <v>61</v>
       </c>
       <c r="B304" t="s" s="2">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="C304" t="s" s="2">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="D304" s="2"/>
     </row>
@@ -6272,10 +6292,10 @@
         <v>61</v>
       </c>
       <c r="B305" t="s" s="2">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="C305" t="s" s="2">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="D305" s="2"/>
     </row>
@@ -6284,10 +6304,10 @@
         <v>61</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="D306" s="2"/>
     </row>
@@ -6296,10 +6316,10 @@
         <v>61</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="D307" s="2"/>
     </row>
@@ -6308,10 +6328,10 @@
         <v>61</v>
       </c>
       <c r="B308" t="s" s="2">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="C308" t="s" s="2">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="D308" s="2"/>
     </row>
@@ -6320,10 +6340,10 @@
         <v>61</v>
       </c>
       <c r="B309" t="s" s="2">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="C309" t="s" s="2">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="D309" s="2"/>
     </row>
@@ -6332,10 +6352,10 @@
         <v>61</v>
       </c>
       <c r="B310" t="s" s="2">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="C310" t="s" s="2">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="D310" s="2"/>
     </row>
@@ -6344,10 +6364,10 @@
         <v>61</v>
       </c>
       <c r="B311" t="s" s="2">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="C311" t="s" s="2">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="D311" s="2"/>
     </row>
@@ -6356,10 +6376,10 @@
         <v>61</v>
       </c>
       <c r="B312" t="s" s="2">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="C312" t="s" s="2">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="D312" s="2"/>
     </row>
@@ -6368,10 +6388,10 @@
         <v>61</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="D313" s="2"/>
     </row>
@@ -6380,10 +6400,10 @@
         <v>61</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="D314" s="2"/>
     </row>
@@ -6392,10 +6412,10 @@
         <v>61</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="D315" s="2"/>
     </row>
@@ -6404,10 +6424,10 @@
         <v>61</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="D316" s="2"/>
     </row>
@@ -6416,10 +6436,10 @@
         <v>61</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="D317" s="2"/>
     </row>
@@ -6428,10 +6448,10 @@
         <v>61</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="D318" s="2"/>
     </row>
@@ -6440,10 +6460,10 @@
         <v>61</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="D319" s="2"/>
     </row>
@@ -6452,10 +6472,10 @@
         <v>61</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D320" s="2"/>
     </row>
@@ -6464,10 +6484,10 @@
         <v>61</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="D321" s="2"/>
     </row>
@@ -6476,10 +6496,10 @@
         <v>61</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="D322" s="2"/>
     </row>
@@ -6488,10 +6508,10 @@
         <v>61</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="D323" s="2"/>
     </row>
@@ -6500,10 +6520,10 @@
         <v>61</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="D324" s="2"/>
     </row>
@@ -6512,10 +6532,10 @@
         <v>61</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="D325" s="2"/>
     </row>
@@ -6524,10 +6544,10 @@
         <v>61</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="D326" s="2"/>
     </row>
@@ -6536,10 +6556,10 @@
         <v>61</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D327" s="2"/>
     </row>
@@ -6548,10 +6568,10 @@
         <v>61</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="D328" s="2"/>
     </row>
@@ -6560,10 +6580,10 @@
         <v>61</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="D329" s="2"/>
     </row>
@@ -6572,10 +6592,10 @@
         <v>61</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="D330" s="2"/>
     </row>

--- a/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R01-EnsembleSavoirFaire-CISIS.xlsx
+++ b/ig/DM-OCTOBRE-2026/CodeSystem-TRE-R01-EnsembleSavoirFaire-CISIS.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260928120000</t>
+    <t>20261102120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-28T12:00:00+01:00</t>
+    <t>2026-11-02T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1738,7 +1738,7 @@
     <t>SM76</t>
   </si>
   <si>
-    <t>Anesthésie-réanimation opt anesthésie-pédiatrique (SM)</t>
+    <t>Anesthésie-réanimation opt réanimation-pédiatrique (SM)</t>
   </si>
   <si>
     <t>SM77</t>
